--- a/travel/2026-10_JIPF83/出張日程表_10月16-18日_日本財政学会.xlsx
+++ b/travel/2026-10_JIPF83/出張日程表_10月16-18日_日本財政学会.xlsx
@@ -1170,7 +1170,7 @@
           <t>東京駅</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="0" t="inlineStr">
         <is>
           <t>東京都内宿泊</t>
         </is>
@@ -1228,7 +1228,7 @@
           <t>神保町駅</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="0" t="inlineStr">
         <is>
           <t>専修大学 神田キャンパス</t>
         </is>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="H15" s="97" t="inlineStr">
         <is>
-          <t>日本財政学会第83回大会（1日目）に参加。自由論題にて研究報告「【報告題目】」</t>
+          <t>日本財政学会第83回大会（1日目）に参加。分科会A-1「外国財政１」、B-1「外国財政２」、シンポジウム、会員総会（～18時30分）</t>
         </is>
       </c>
       <c r="I15" s="28" t="inlineStr">
@@ -1265,7 +1265,11 @@
     <row r="17" ht="19.9" customFormat="1" customHeight="1" s="3">
       <c r="A17" s="61" t="n"/>
       <c r="C17" s="62" t="n"/>
-      <c r="D17" s="58" t="n"/>
+      <c r="D17" s="58" t="inlineStr">
+        <is>
+          <t>18時45分頃</t>
+        </is>
+      </c>
       <c r="E17" s="57" t="inlineStr">
         <is>
           <t>神保町駅</t>
@@ -1310,7 +1314,7 @@
           <t>神保町駅</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="0" t="inlineStr">
         <is>
           <t>専修大学 神田キャンパス</t>
         </is>
@@ -1320,7 +1324,7 @@
       </c>
       <c r="H19" s="99" t="inlineStr">
         <is>
-          <t>日本財政学会第83回大会（2日目）に参加（15時終了）</t>
+          <t>日本財政学会第83回大会（2日目）。分科会C-3「地方財政３」（9時30分～11時30分）にて研究報告「地方財政レジリエンス論の理論的再構成ーフィンランドを通じた政府間財政関係論の再検討」。午後は企画④「地域課題の創造的解決の財政論」に参加（～14時40分）</t>
         </is>
       </c>
       <c r="I19" s="28" t="inlineStr">
@@ -1330,7 +1334,7 @@
       </c>
       <c r="J19" s="39" t="inlineStr">
         <is>
-          <t>10号館</t>
+          <t>教室10081</t>
         </is>
       </c>
     </row>
@@ -1349,7 +1353,7 @@
       <c r="C21" s="62" t="n"/>
       <c r="D21" s="58" t="inlineStr">
         <is>
-          <t>15時半頃</t>
+          <t>15時頃</t>
         </is>
       </c>
       <c r="E21" s="28" t="inlineStr">
@@ -1368,7 +1372,7 @@
       <c r="C22" s="62" t="n"/>
       <c r="D22" s="62" t="inlineStr">
         <is>
-          <t>16時頃</t>
+          <t>15時半頃</t>
         </is>
       </c>
       <c r="E22" s="28" t="inlineStr">
@@ -1386,7 +1390,7 @@
       <c r="C23" s="62" t="n"/>
       <c r="D23" s="62" t="inlineStr">
         <is>
-          <t>19時半頃</t>
+          <t>19時頃</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
